--- a/AAII_Financials/Quarterly/CHMG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHMG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>CHMG</t>
   </si>
@@ -656,232 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E8" s="3">
         <v>29000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>27800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>18500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16400</v>
-      </c>
-      <c r="S8" s="3">
-        <v>16800</v>
       </c>
       <c r="T8" s="3">
         <v>16800</v>
       </c>
       <c r="U8" s="3">
-        <v>16700</v>
+        <v>16800</v>
       </c>
       <c r="V8" s="3">
         <v>16700</v>
       </c>
       <c r="W8" s="3">
+        <v>16700</v>
+      </c>
+      <c r="X8" s="3">
         <v>16900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>15900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>15700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>15600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>15500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14700</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>14300</v>
       </c>
       <c r="AE8" s="3">
         <v>14300</v>
       </c>
       <c r="AF8" s="3">
+        <v>14300</v>
+      </c>
+      <c r="AG8" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,8 +978,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1407,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>-100</v>
@@ -1428,7 +1450,7 @@
         <v>-100</v>
       </c>
       <c r="T15" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="U15" s="3">
         <v>-200</v>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E17" s="3">
         <v>11400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>-800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1200</v>
-      </c>
-      <c r="M17" s="3">
-        <v>700</v>
       </c>
       <c r="N17" s="3">
         <v>700</v>
       </c>
       <c r="O17" s="3">
+        <v>700</v>
+      </c>
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E18" s="3">
         <v>17600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>14700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>14700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8500</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>13500</v>
       </c>
       <c r="AC18" s="3">
         <v>13500</v>
       </c>
       <c r="AD18" s="3">
+        <v>13500</v>
+      </c>
+      <c r="AE18" s="3">
         <v>12400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>12900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,180 +1747,184 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-10400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-9000</v>
       </c>
       <c r="J20" s="3">
         <v>-9000</v>
       </c>
       <c r="K20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="L20" s="3">
         <v>-8600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-11700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-9300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-8100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E21" s="3">
         <v>10200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6500</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>5400</v>
       </c>
       <c r="AD21" s="3">
         <v>5400</v>
@@ -1897,10 +1933,13 @@
         <v>5400</v>
       </c>
       <c r="AF21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AG21" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,180 +2030,186 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E23" s="3">
         <v>9700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6500</v>
-      </c>
-      <c r="P23" s="3">
-        <v>7200</v>
       </c>
       <c r="Q23" s="3">
         <v>7200</v>
       </c>
       <c r="R23" s="3">
+        <v>7200</v>
+      </c>
+      <c r="S23" s="3">
         <v>3000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1700</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>1300</v>
       </c>
       <c r="AD24" s="3">
         <v>1300</v>
@@ -2173,10 +2218,13 @@
         <v>1300</v>
       </c>
       <c r="AF24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AG24" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,88 +2315,91 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E26" s="3">
         <v>7600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3700</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>3000</v>
       </c>
       <c r="AD26" s="3">
         <v>3000</v>
@@ -2357,90 +2408,93 @@
         <v>3000</v>
       </c>
       <c r="AF26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG26" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E27" s="3">
         <v>7600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3700</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>3000</v>
       </c>
       <c r="AD27" s="3">
         <v>3000</v>
@@ -2449,10 +2503,13 @@
         <v>3000</v>
       </c>
       <c r="AF27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG27" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2584,8 +2644,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>5</v>
@@ -2605,24 +2665,24 @@
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>400</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,180 +2885,186 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E32" s="3">
         <v>7800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>10400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>9000</v>
       </c>
       <c r="J32" s="3">
         <v>9000</v>
       </c>
       <c r="K32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="L32" s="3">
         <v>8600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>11700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>9300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>9700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>8700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>8100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>9300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>8200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>8700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E33" s="3">
         <v>7600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3700</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>3000</v>
       </c>
       <c r="AD33" s="3">
         <v>3000</v>
@@ -3001,10 +3073,13 @@
         <v>3000</v>
       </c>
       <c r="AF33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG33" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,88 +3170,91 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E35" s="3">
         <v>7600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3700</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>3000</v>
       </c>
       <c r="AD35" s="3">
         <v>3000</v>
@@ -3185,107 +3263,113 @@
         <v>3000</v>
       </c>
       <c r="AF35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG35" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,192 +3437,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E41" s="3">
         <v>52600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>21800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>28700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>27500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>25200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>36500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>32600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>28200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>33000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>31800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>30800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>25500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>34600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>26700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>26300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>28200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>35300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E42" s="3">
         <v>60000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>61500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>40200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>61900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>14000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>47300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>36400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>32900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>129600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>82200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>117700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>129600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>120000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>99800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>112900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>86900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>100800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>100100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>85200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>8600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>26200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>42500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>103800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>50800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +3910,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,83 +4005,86 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="E47" s="3">
         <v>2800</v>
       </c>
       <c r="F47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G47" s="3">
         <v>2900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3000</v>
-      </c>
-      <c r="L47" s="3">
-        <v>2900</v>
       </c>
       <c r="M47" s="3">
         <v>2900</v>
       </c>
       <c r="N47" s="3">
+        <v>2900</v>
+      </c>
+      <c r="O47" s="3">
         <v>2700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2200</v>
-      </c>
-      <c r="T47" s="3">
-        <v>2100</v>
       </c>
       <c r="U47" s="3">
         <v>2100</v>
       </c>
       <c r="V47" s="3">
+        <v>2100</v>
+      </c>
+      <c r="W47" s="3">
         <v>2000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2200</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3996,100 +4100,106 @@
       <c r="AF47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E48" s="3">
         <v>20900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>29000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>29600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>30400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>31000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>31800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>32700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>25000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>25500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>26000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>26100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>27400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>27800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>28200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>28900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4118,70 +4228,73 @@
         <v>21800</v>
       </c>
       <c r="L49" s="3">
-        <v>21900</v>
+        <v>21800</v>
       </c>
       <c r="M49" s="3">
         <v>21900</v>
       </c>
       <c r="N49" s="3">
+        <v>21900</v>
+      </c>
+      <c r="O49" s="3">
         <v>22000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>22300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>22700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>22900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>23900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>24100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>24300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>24500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>24800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4480,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4456,8 +4575,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2710500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2707800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2674700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2654200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2645600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2551400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2449900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2474900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2418500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2417700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2380700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2442500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2279500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2165000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2050900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1841300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1787800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1793600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1753000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1769600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1755300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1753900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1710200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1700000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1707600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1731700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1718600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1736100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1657200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1728900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4837,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E57" s="3">
         <v>20700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>51000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>34700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>27600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>26000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>29700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>30900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>32100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>29600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>21600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>19800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>15800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>14900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>15600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>14700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,73 +5025,76 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E59" s="3">
         <v>7500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1300</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1200</v>
       </c>
       <c r="Y59" s="3">
         <v>1200</v>
@@ -4984,8 +5120,11 @@
       <c r="AF59" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,8 +5215,11 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5085,91 +5227,94 @@
         <v>3100</v>
       </c>
       <c r="E61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F61" s="3">
         <v>3200</v>
-      </c>
-      <c r="F61" s="3">
-        <v>3300</v>
       </c>
       <c r="G61" s="3">
         <v>3300</v>
       </c>
       <c r="H61" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I61" s="3">
         <v>3400</v>
-      </c>
-      <c r="I61" s="3">
-        <v>3500</v>
       </c>
       <c r="J61" s="3">
         <v>3500</v>
       </c>
       <c r="K61" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L61" s="3">
         <v>3600</v>
-      </c>
-      <c r="L61" s="3">
-        <v>3700</v>
       </c>
       <c r="M61" s="3">
         <v>3700</v>
       </c>
       <c r="N61" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="O61" s="3">
         <v>3800</v>
       </c>
       <c r="P61" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Q61" s="3">
         <v>3900</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>4000</v>
       </c>
       <c r="R61" s="3">
         <v>4000</v>
       </c>
       <c r="S61" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="T61" s="3">
         <v>4100</v>
       </c>
       <c r="U61" s="3">
+        <v>4100</v>
+      </c>
+      <c r="V61" s="3">
         <v>4200</v>
-      </c>
-      <c r="V61" s="3">
-        <v>4300</v>
       </c>
       <c r="W61" s="3">
         <v>4300</v>
       </c>
       <c r="X61" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="Y61" s="3">
         <v>4400</v>
       </c>
       <c r="Z61" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="AA61" s="3">
         <v>4500</v>
       </c>
       <c r="AB61" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="AC61" s="3">
         <v>4600</v>
       </c>
       <c r="AD61" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="AE61" s="3">
         <v>4700</v>
       </c>
       <c r="AF61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AG61" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2515300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2537800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2497200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2476800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2479200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2395900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2275200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2289400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2207000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2211500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2176700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2247700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2079800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1968000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1856300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1650900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1605200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1611600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1574600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1598000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1590300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1597400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1558400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1549700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1557800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1577400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1566600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1587800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1513400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1584100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>229900</v>
+      </c>
+      <c r="E72" s="3">
         <v>227600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>221400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>216600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>211900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>205900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>200900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>194300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>188900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>183900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>178700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>173300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>168000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>164000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>159500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>154900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>153700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>150800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>150100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>146300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>143100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>138700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>133000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>131700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>128500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>130000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>127600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>125900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>124100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>122400</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>195200</v>
+      </c>
+      <c r="E76" s="3">
         <v>170100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>177400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>177300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>166400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>155500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>174700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>185500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>211500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>206100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>204000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>194800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>199700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>197000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>194600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>190400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>182600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>182000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>178400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>171500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>165000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>156500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>151800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>150300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>149800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>154300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>152000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>148300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>143700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>144800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,185 +6770,191 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E81" s="3">
         <v>7600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3700</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>3000</v>
       </c>
       <c r="AD81" s="3">
         <v>3000</v>
@@ -6769,10 +6963,13 @@
         <v>3000</v>
       </c>
       <c r="AF81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG81" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6826,7 +7024,7 @@
         <v>500</v>
       </c>
       <c r="I83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J83" s="3">
         <v>600</v>
@@ -6838,10 +7036,10 @@
         <v>600</v>
       </c>
       <c r="M83" s="3">
+        <v>600</v>
+      </c>
+      <c r="N83" s="3">
         <v>700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>800</v>
       </c>
       <c r="O83" s="3">
         <v>800</v>
@@ -6850,7 +7048,7 @@
         <v>800</v>
       </c>
       <c r="Q83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="R83" s="3">
         <v>900</v>
@@ -6862,7 +7060,7 @@
         <v>900</v>
       </c>
       <c r="U83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="V83" s="3">
         <v>1000</v>
@@ -6874,7 +7072,7 @@
         <v>1000</v>
       </c>
       <c r="Y83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="Z83" s="3">
         <v>1100</v>
@@ -6886,7 +7084,7 @@
         <v>1100</v>
       </c>
       <c r="AC83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AD83" s="3">
         <v>1200</v>
@@ -6897,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E89" s="3">
         <v>9400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8900</v>
-      </c>
-      <c r="L89" s="3">
-        <v>9200</v>
       </c>
       <c r="M89" s="3">
         <v>9200</v>
       </c>
       <c r="N89" s="3">
+        <v>9200</v>
+      </c>
+      <c r="O89" s="3">
         <v>8200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7492,52 +7712,52 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-200</v>
       </c>
       <c r="P91" s="3">
         <v>-200</v>
       </c>
       <c r="Q91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
@@ -7546,37 +7766,40 @@
         <v>-100</v>
       </c>
       <c r="W91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="X91" s="3">
         <v>-300</v>
       </c>
       <c r="Y91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-77000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-105300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-45000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-37800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-38500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-130400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-159800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-121100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-196200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-23400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>11100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>16300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>32600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>3400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-24600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-29400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-21200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7903,22 +8136,22 @@
         <v>-1500</v>
       </c>
       <c r="H96" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="I96" s="3">
         <v>-1400</v>
       </c>
       <c r="J96" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-1400</v>
       </c>
       <c r="L96" s="3">
         <v>-1400</v>
       </c>
       <c r="M96" s="3">
-        <v>-1200</v>
+        <v>-1400</v>
       </c>
       <c r="N96" s="3">
         <v>-1200</v>
@@ -7930,7 +8163,7 @@
         <v>-1200</v>
       </c>
       <c r="Q96" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="R96" s="3">
         <v>-1300</v>
@@ -7951,7 +8184,7 @@
         <v>-1300</v>
       </c>
       <c r="X96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="Y96" s="3">
         <v>-1200</v>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8495,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E100" s="3">
         <v>31100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>17200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>88100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>103200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-22300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>77500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>34200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-73600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>170700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>109700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>110200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>198900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>35100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>34200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-26600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>37000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>8600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>8900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-23700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>74400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-66200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="E102" s="3">
         <v>21400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-35700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>38500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-34700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>48500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-41400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>10700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>22600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-24400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>29800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>16100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>79100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-25600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-61100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>51500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-61300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>28200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHMG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHMG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>CHMG</t>
   </si>
@@ -656,238 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E8" s="3">
         <v>30000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>29000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>27800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>26200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16400</v>
-      </c>
-      <c r="T8" s="3">
-        <v>16800</v>
       </c>
       <c r="U8" s="3">
         <v>16800</v>
       </c>
       <c r="V8" s="3">
-        <v>16700</v>
+        <v>16800</v>
       </c>
       <c r="W8" s="3">
         <v>16700</v>
       </c>
       <c r="X8" s="3">
+        <v>16700</v>
+      </c>
+      <c r="Y8" s="3">
         <v>16900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>15900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>15700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>15600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>15500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14700</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>14300</v>
       </c>
       <c r="AF8" s="3">
         <v>14300</v>
       </c>
       <c r="AG8" s="3">
+        <v>14300</v>
+      </c>
+      <c r="AH8" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1396,13 +1416,16 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1432,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3">
         <v>-100</v>
@@ -1453,7 +1476,7 @@
         <v>-100</v>
       </c>
       <c r="U15" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="V15" s="3">
         <v>-200</v>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E17" s="3">
         <v>14400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1200</v>
-      </c>
-      <c r="N17" s="3">
-        <v>700</v>
       </c>
       <c r="O17" s="3">
         <v>700</v>
       </c>
       <c r="P17" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E18" s="3">
         <v>15600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>17600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>19800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>17700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>15000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>15000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>14100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>14700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8500</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>13500</v>
       </c>
       <c r="AD18" s="3">
         <v>13500</v>
       </c>
       <c r="AE18" s="3">
+        <v>13500</v>
+      </c>
+      <c r="AF18" s="3">
         <v>12400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>12900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,186 +1781,190 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-10500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-9000</v>
       </c>
       <c r="K20" s="3">
         <v>-9000</v>
       </c>
       <c r="L20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="M20" s="3">
         <v>-8600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-10000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-8600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E21" s="3">
         <v>5100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6500</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>5400</v>
       </c>
       <c r="AE21" s="3">
         <v>5400</v>
@@ -1936,10 +1973,13 @@
         <v>5400</v>
       </c>
       <c r="AG21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AH21" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2033,186 +2073,192 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E23" s="3">
         <v>4600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6500</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>7200</v>
       </c>
       <c r="R23" s="3">
         <v>7200</v>
       </c>
       <c r="S23" s="3">
+        <v>7200</v>
+      </c>
+      <c r="T23" s="3">
         <v>3000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1700</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>1300</v>
       </c>
       <c r="AE24" s="3">
         <v>1300</v>
@@ -2221,10 +2267,13 @@
         <v>1300</v>
       </c>
       <c r="AG24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,91 +2367,94 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E26" s="3">
         <v>3800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3700</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>3000</v>
       </c>
       <c r="AE26" s="3">
         <v>3000</v>
@@ -2411,93 +2463,96 @@
         <v>3000</v>
       </c>
       <c r="AG26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AH26" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E27" s="3">
         <v>3800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3700</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>3000</v>
       </c>
       <c r="AE27" s="3">
         <v>3000</v>
@@ -2506,10 +2561,13 @@
         <v>3000</v>
       </c>
       <c r="AG27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AH27" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2647,8 +2708,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
@@ -2668,24 +2729,24 @@
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>400</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,186 +2955,192 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E32" s="3">
         <v>10900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>10500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>9000</v>
       </c>
       <c r="K32" s="3">
         <v>9000</v>
       </c>
       <c r="L32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="M32" s="3">
         <v>8600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>10000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>8600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>9300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>9700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>8700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>8100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>9300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>8200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>8700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E33" s="3">
         <v>3800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3700</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>3000</v>
       </c>
       <c r="AE33" s="3">
         <v>3000</v>
@@ -3076,10 +3149,13 @@
         <v>3000</v>
       </c>
       <c r="AG33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AH33" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,91 +3249,94 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E35" s="3">
         <v>3800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3700</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>3000</v>
       </c>
       <c r="AE35" s="3">
         <v>3000</v>
@@ -3266,110 +3345,116 @@
         <v>3000</v>
       </c>
       <c r="AG35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AH35" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,198 +3524,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E41" s="3">
         <v>22200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>29300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>27400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>28700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>27500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>25200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>36500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>32600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>28200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>33000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>31800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>30800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>25500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>28000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>34600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>26700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>26300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>28200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>35300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E42" s="3">
         <v>44000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>60000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>61500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>40200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>61900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>47300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>36400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>32900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>129600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>82200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>117700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>129600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>120000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>99800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>112900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>86900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>100800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>100100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>85200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>9800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>8600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>9500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>26200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>42500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>103800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>50800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3723,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3913,8 +4012,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4008,86 +4110,89 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E47" s="3">
         <v>3000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2800</v>
       </c>
       <c r="F47" s="3">
         <v>2800</v>
       </c>
       <c r="G47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H47" s="3">
         <v>2900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3000</v>
-      </c>
-      <c r="M47" s="3">
-        <v>2900</v>
       </c>
       <c r="N47" s="3">
         <v>2900</v>
       </c>
       <c r="O47" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P47" s="3">
         <v>2700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2200</v>
-      </c>
-      <c r="U47" s="3">
-        <v>2100</v>
       </c>
       <c r="V47" s="3">
         <v>2100</v>
       </c>
       <c r="W47" s="3">
+        <v>2100</v>
+      </c>
+      <c r="X47" s="3">
         <v>2000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2200</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4103,8 +4208,11 @@
       <c r="AG47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4112,94 +4220,97 @@
         <v>20200</v>
       </c>
       <c r="E48" s="3">
+        <v>20200</v>
+      </c>
+      <c r="F48" s="3">
         <v>20900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>29000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>29600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>30400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>31000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>31800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>32700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>25000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>25500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>26000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>26700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>27400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>27800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>28200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>28900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4231,70 +4342,73 @@
         <v>21800</v>
       </c>
       <c r="M49" s="3">
-        <v>21900</v>
+        <v>21800</v>
       </c>
       <c r="N49" s="3">
         <v>21900</v>
       </c>
       <c r="O49" s="3">
+        <v>21900</v>
+      </c>
+      <c r="P49" s="3">
         <v>22000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>22200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>22600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>22700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>22900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>23700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>23900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>24100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>24300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>24500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>24800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2784900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2710500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2707800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2674700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2654200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2645600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2551400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2449900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2474900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2418500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2417700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2380700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2442500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2279500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2165000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2050900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1841300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1787800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1793600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1753000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1769600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1755300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1753900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1710200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1700000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1707600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1731700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1718600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1736100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1657200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1728900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,103 +4968,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E57" s="3">
         <v>19600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>51000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>34700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>25400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>26000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>29700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>30900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>32100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>29600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>21600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>19800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>17600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>14900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>14900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>15600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>14700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>13400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>14400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5028,76 +5162,79 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E59" s="3">
         <v>7300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1300</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>1200</v>
       </c>
       <c r="Z59" s="3">
         <v>1200</v>
@@ -5123,8 +5260,11 @@
       <c r="AG59" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5218,103 +5358,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="E61" s="3">
         <v>3100</v>
       </c>
       <c r="F61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G61" s="3">
         <v>3200</v>
-      </c>
-      <c r="G61" s="3">
-        <v>3300</v>
       </c>
       <c r="H61" s="3">
         <v>3300</v>
       </c>
       <c r="I61" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J61" s="3">
         <v>3400</v>
-      </c>
-      <c r="J61" s="3">
-        <v>3500</v>
       </c>
       <c r="K61" s="3">
         <v>3500</v>
       </c>
       <c r="L61" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M61" s="3">
         <v>3600</v>
-      </c>
-      <c r="M61" s="3">
-        <v>3700</v>
       </c>
       <c r="N61" s="3">
         <v>3700</v>
       </c>
       <c r="O61" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="P61" s="3">
         <v>3800</v>
       </c>
       <c r="Q61" s="3">
+        <v>3800</v>
+      </c>
+      <c r="R61" s="3">
         <v>3900</v>
-      </c>
-      <c r="R61" s="3">
-        <v>4000</v>
       </c>
       <c r="S61" s="3">
         <v>4000</v>
       </c>
       <c r="T61" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="U61" s="3">
         <v>4100</v>
       </c>
       <c r="V61" s="3">
+        <v>4100</v>
+      </c>
+      <c r="W61" s="3">
         <v>4200</v>
-      </c>
-      <c r="W61" s="3">
-        <v>4300</v>
       </c>
       <c r="X61" s="3">
         <v>4300</v>
       </c>
       <c r="Y61" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="Z61" s="3">
         <v>4400</v>
       </c>
       <c r="AA61" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="AB61" s="3">
         <v>4500</v>
       </c>
       <c r="AC61" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="AD61" s="3">
         <v>4600</v>
       </c>
       <c r="AE61" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="AF61" s="3">
         <v>4700</v>
       </c>
       <c r="AG61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AH61" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2587800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2515300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2537800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2497200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2476800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2479200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2395900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2275200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2289400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2207000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2211500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2176700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2247700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2079800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1968000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1856300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1650900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1605200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1611600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1574600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1598000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1590300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1597400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1558400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1549700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1557800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1577400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1566600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1587800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1513400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1584100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>235500</v>
+      </c>
+      <c r="E72" s="3">
         <v>229900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>227600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>221400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>216600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>211900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>205900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>200900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>194300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>188900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>183900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>178700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>173300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>168000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>164000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>159500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>154900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>153700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>150800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>150100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>146300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>143100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>138700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>133000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>131700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>128500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>130000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>127600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>125900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>124100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>122400</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>197100</v>
+      </c>
+      <c r="E76" s="3">
         <v>195200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>170100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>177400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>177300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>166400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>155500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>174700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>185500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>211500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>206100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>204000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>194800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>199700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>197000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>194600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>190400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>182600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>182000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>178400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>171500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>165000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>156500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>151800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>150300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>149800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>154300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>152000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>148300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>143700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>144800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,191 +6962,197 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E81" s="3">
         <v>3800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3700</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>3000</v>
       </c>
       <c r="AE81" s="3">
         <v>3000</v>
@@ -6966,10 +7161,13 @@
         <v>3000</v>
       </c>
       <c r="AG81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AH81" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7027,7 +7226,7 @@
         <v>500</v>
       </c>
       <c r="J83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
@@ -7039,10 +7238,10 @@
         <v>600</v>
       </c>
       <c r="N83" s="3">
+        <v>600</v>
+      </c>
+      <c r="O83" s="3">
         <v>700</v>
-      </c>
-      <c r="O83" s="3">
-        <v>800</v>
       </c>
       <c r="P83" s="3">
         <v>800</v>
@@ -7051,7 +7250,7 @@
         <v>800</v>
       </c>
       <c r="R83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="S83" s="3">
         <v>900</v>
@@ -7063,7 +7262,7 @@
         <v>900</v>
       </c>
       <c r="V83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="W83" s="3">
         <v>1000</v>
@@ -7075,7 +7274,7 @@
         <v>1000</v>
       </c>
       <c r="Z83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="AA83" s="3">
         <v>1100</v>
@@ -7087,7 +7286,7 @@
         <v>1100</v>
       </c>
       <c r="AD83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AE83" s="3">
         <v>1200</v>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E89" s="3">
         <v>3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8900</v>
-      </c>
-      <c r="M89" s="3">
-        <v>9200</v>
       </c>
       <c r="N89" s="3">
         <v>9200</v>
       </c>
       <c r="O89" s="3">
+        <v>9200</v>
+      </c>
+      <c r="P89" s="3">
         <v>8200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,64 +7923,65 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-200</v>
       </c>
       <c r="Q91" s="3">
         <v>-200</v>
       </c>
       <c r="R91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
@@ -7769,37 +7990,40 @@
         <v>-100</v>
       </c>
       <c r="X91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="Y91" s="3">
         <v>-300</v>
       </c>
       <c r="Z91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-77000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-105300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-45000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-37800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-38500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-130400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-159800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-121100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-196200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-18800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>11100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>16300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>32600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>3400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-24600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-29400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>2500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-21200</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8139,22 +8373,22 @@
         <v>-1500</v>
       </c>
       <c r="I96" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="J96" s="3">
         <v>-1400</v>
       </c>
       <c r="K96" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L96" s="3">
         <v>-1500</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-1400</v>
       </c>
       <c r="M96" s="3">
         <v>-1400</v>
       </c>
       <c r="N96" s="3">
-        <v>-1200</v>
+        <v>-1400</v>
       </c>
       <c r="O96" s="3">
         <v>-1200</v>
@@ -8166,7 +8400,7 @@
         <v>-1200</v>
       </c>
       <c r="R96" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="S96" s="3">
         <v>-1300</v>
@@ -8187,7 +8421,7 @@
         <v>-1300</v>
       </c>
       <c r="Y96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="Z96" s="3">
         <v>-1200</v>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,103 +8741,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>31100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>88100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>103200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-22300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>77500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>34200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-73600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>170700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>109700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>110200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>198900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>35100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>34200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-26600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>37000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>8600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>8900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-23700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>74400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-66200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-38700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-35700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>38500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-34700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>48500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-41400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>10700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>22600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-24400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>29800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>16100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>79100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-25600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-61100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>51500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-61300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>28200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHMG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHMG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>CHMG</t>
   </si>
@@ -656,245 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E8" s="3">
         <v>31200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>27800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>26200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16400</v>
-      </c>
-      <c r="U8" s="3">
-        <v>16800</v>
       </c>
       <c r="V8" s="3">
         <v>16800</v>
       </c>
       <c r="W8" s="3">
-        <v>16700</v>
+        <v>16800</v>
       </c>
       <c r="X8" s="3">
         <v>16700</v>
       </c>
       <c r="Y8" s="3">
+        <v>16700</v>
+      </c>
+      <c r="Z8" s="3">
         <v>16900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>15900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>15700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>15600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>15500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14700</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>14300</v>
       </c>
       <c r="AG8" s="3">
         <v>14300</v>
       </c>
       <c r="AH8" s="3">
+        <v>14300</v>
+      </c>
+      <c r="AI8" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1419,16 +1439,19 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -1458,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3">
         <v>-100</v>
@@ -1479,7 +1502,7 @@
         <v>-100</v>
       </c>
       <c r="V15" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="W15" s="3">
         <v>-200</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E17" s="3">
         <v>11100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1200</v>
-      </c>
-      <c r="O17" s="3">
-        <v>700</v>
       </c>
       <c r="P17" s="3">
         <v>700</v>
       </c>
       <c r="Q17" s="3">
+        <v>700</v>
+      </c>
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E18" s="3">
         <v>20100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>19600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>16100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>14100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8500</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>13500</v>
       </c>
       <c r="AE18" s="3">
         <v>13500</v>
       </c>
       <c r="AF18" s="3">
+        <v>13500</v>
+      </c>
+      <c r="AG18" s="3">
         <v>12400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>12900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,192 +1815,196 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-11000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-9000</v>
       </c>
       <c r="L20" s="3">
         <v>-9000</v>
       </c>
       <c r="M20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N20" s="3">
         <v>-8600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-10000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-11700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-9800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-8800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-8100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-8200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E21" s="3">
         <v>9600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6500</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>5400</v>
       </c>
       <c r="AF21" s="3">
         <v>5400</v>
@@ -1976,10 +2013,13 @@
         <v>5400</v>
       </c>
       <c r="AH21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AI21" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,192 +2116,198 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E23" s="3">
         <v>9100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6500</v>
-      </c>
-      <c r="R23" s="3">
-        <v>7200</v>
       </c>
       <c r="S23" s="3">
         <v>7200</v>
       </c>
       <c r="T23" s="3">
+        <v>7200</v>
+      </c>
+      <c r="U23" s="3">
         <v>3000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1700</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>1300</v>
       </c>
       <c r="AF24" s="3">
         <v>1300</v>
@@ -2270,10 +2316,13 @@
         <v>1300</v>
       </c>
       <c r="AH24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AI24" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,94 +2419,97 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3700</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>3000</v>
       </c>
       <c r="AF26" s="3">
         <v>3000</v>
@@ -2466,96 +2518,99 @@
         <v>3000</v>
       </c>
       <c r="AH26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AI26" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3700</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>3000</v>
       </c>
       <c r="AF27" s="3">
         <v>3000</v>
@@ -2564,10 +2619,13 @@
         <v>3000</v>
       </c>
       <c r="AH27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AI27" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2711,8 +2772,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>5</v>
@@ -2732,24 +2793,24 @@
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
         <v>400</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,192 +3025,198 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E32" s="3">
         <v>11000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>9000</v>
       </c>
       <c r="L32" s="3">
         <v>9000</v>
       </c>
       <c r="M32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="N32" s="3">
         <v>8600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>10000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>11700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>9800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>8800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>8600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>9300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>9700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>8700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>7700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>8100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>9300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>8200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>8700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3700</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>3000</v>
       </c>
       <c r="AF33" s="3">
         <v>3000</v>
@@ -3152,10 +3225,13 @@
         <v>3000</v>
       </c>
       <c r="AH33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AI33" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,94 +3328,97 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3700</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>3000</v>
       </c>
       <c r="AF35" s="3">
         <v>3000</v>
@@ -3348,113 +3427,119 @@
         <v>3000</v>
       </c>
       <c r="AH35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AI35" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,204 +3611,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E41" s="3">
         <v>23000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>27400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>30600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>35300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>28700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>27500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>25200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>36500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>32600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>28200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>33000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>31800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>30800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>25500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>28000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>34600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>26700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>26300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>28200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>35300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E42" s="3">
         <v>101800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>44000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>60000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>61500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>40200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>61900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>14000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>47300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>36400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>32900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>129600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>82200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>117700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>129600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>120000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>99800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>112900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>86900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>100800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>100100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>85200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>8600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>9500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>26200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>42500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>103800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>50800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4015,8 +4114,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4113,8 +4215,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4122,80 +4227,80 @@
         <v>3100</v>
       </c>
       <c r="E47" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F47" s="3">
         <v>3000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>2800</v>
       </c>
       <c r="G47" s="3">
         <v>2800</v>
       </c>
       <c r="H47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I47" s="3">
         <v>2900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2900</v>
       </c>
       <c r="O47" s="3">
         <v>2900</v>
       </c>
       <c r="P47" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q47" s="3">
         <v>2700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2200</v>
-      </c>
-      <c r="V47" s="3">
-        <v>2100</v>
       </c>
       <c r="W47" s="3">
         <v>2100</v>
       </c>
       <c r="X47" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Y47" s="3">
         <v>2000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2200</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4211,106 +4316,112 @@
       <c r="AH47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>20200</v>
+        <v>20600</v>
       </c>
       <c r="E48" s="3">
         <v>20200</v>
       </c>
       <c r="F48" s="3">
+        <v>20200</v>
+      </c>
+      <c r="G48" s="3">
         <v>20900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>28400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>29000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>29600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>30400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>31000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>31800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>32700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>25000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>25500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>26100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>26700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>27400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>27800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>28200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>28900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4345,70 +4456,73 @@
         <v>21800</v>
       </c>
       <c r="N49" s="3">
-        <v>21900</v>
+        <v>21800</v>
       </c>
       <c r="O49" s="3">
         <v>21900</v>
       </c>
       <c r="P49" s="3">
+        <v>21900</v>
+      </c>
+      <c r="Q49" s="3">
         <v>22000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>22100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>22400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>22600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>22700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>22900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>23500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>23700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>23900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>24100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>24300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>24500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>24800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2755800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2784900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2710500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2707800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2674700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2654200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2645600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2551400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2449900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2474900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2418500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2417700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2380700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2442500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2279500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2165000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2050900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1841300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1787800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1793600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1753000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1769600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1755300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1753900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1710200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1700000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1707600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1731700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1718600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1736100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1657200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1728900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E57" s="3">
         <v>20500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>51000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>34700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>25400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>26000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>29700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>30900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>32100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>29600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>19600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>21600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>19800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>17600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>15800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>14900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>15800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>14900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>15600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>14400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5165,79 +5299,82 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E59" s="3">
         <v>7700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1300</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>1200</v>
       </c>
       <c r="AA59" s="3">
         <v>1200</v>
@@ -5263,8 +5400,11 @@
       <c r="AH59" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5361,106 +5501,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E61" s="3">
         <v>3000</v>
-      </c>
-      <c r="E61" s="3">
-        <v>3100</v>
       </c>
       <c r="F61" s="3">
         <v>3100</v>
       </c>
       <c r="G61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H61" s="3">
         <v>3200</v>
-      </c>
-      <c r="H61" s="3">
-        <v>3300</v>
       </c>
       <c r="I61" s="3">
         <v>3300</v>
       </c>
       <c r="J61" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K61" s="3">
         <v>3400</v>
-      </c>
-      <c r="K61" s="3">
-        <v>3500</v>
       </c>
       <c r="L61" s="3">
         <v>3500</v>
       </c>
       <c r="M61" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N61" s="3">
         <v>3600</v>
-      </c>
-      <c r="N61" s="3">
-        <v>3700</v>
       </c>
       <c r="O61" s="3">
         <v>3700</v>
       </c>
       <c r="P61" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="Q61" s="3">
         <v>3800</v>
       </c>
       <c r="R61" s="3">
+        <v>3800</v>
+      </c>
+      <c r="S61" s="3">
         <v>3900</v>
-      </c>
-      <c r="S61" s="3">
-        <v>4000</v>
       </c>
       <c r="T61" s="3">
         <v>4000</v>
       </c>
       <c r="U61" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="V61" s="3">
         <v>4100</v>
       </c>
       <c r="W61" s="3">
+        <v>4100</v>
+      </c>
+      <c r="X61" s="3">
         <v>4200</v>
-      </c>
-      <c r="X61" s="3">
-        <v>4300</v>
       </c>
       <c r="Y61" s="3">
         <v>4300</v>
       </c>
       <c r="Z61" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="AA61" s="3">
         <v>4400</v>
       </c>
       <c r="AB61" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="AC61" s="3">
         <v>4500</v>
       </c>
       <c r="AD61" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="AE61" s="3">
         <v>4600</v>
       </c>
       <c r="AF61" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="AG61" s="3">
         <v>4700</v>
       </c>
       <c r="AH61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AI61" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2554600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2587800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2515300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2537800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2497200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2476800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2479200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2395900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2275200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2289400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2207000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2211500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2176700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2247700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2079800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1968000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1856300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1650900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1605200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1611600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1574600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1598000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1590300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1597400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1558400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1549700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1557800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1577400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1566600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1587800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1513400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1584100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>239000</v>
+      </c>
+      <c r="E72" s="3">
         <v>235500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>229900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>227600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>221400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>216600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>211900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>205900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>200900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>194300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>188900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>183900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>178700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>173300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>168000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>164000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>159500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>154900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>153700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>150800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>150100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>146300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>143100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>138700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>133000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>131700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>128500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>130000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>127600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>125900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>124100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>122400</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>201200</v>
+      </c>
+      <c r="E76" s="3">
         <v>197100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>195200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>170100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>177400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>177300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>166400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>155500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>174700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>185500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>211500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>206100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>204000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>194800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>199700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>197000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>194600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>190400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>182600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>182000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>178400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>171500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>165000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>156500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>151800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>150300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>149800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>154300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>152000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>148300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>143700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>144800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,197 +7154,203 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3700</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>3000</v>
       </c>
       <c r="AF81" s="3">
         <v>3000</v>
@@ -7164,10 +7359,13 @@
         <v>3000</v>
       </c>
       <c r="AH81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AI81" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7229,7 +7428,7 @@
         <v>500</v>
       </c>
       <c r="K83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="L83" s="3">
         <v>600</v>
@@ -7241,10 +7440,10 @@
         <v>600</v>
       </c>
       <c r="O83" s="3">
+        <v>600</v>
+      </c>
+      <c r="P83" s="3">
         <v>700</v>
-      </c>
-      <c r="P83" s="3">
-        <v>800</v>
       </c>
       <c r="Q83" s="3">
         <v>800</v>
@@ -7253,7 +7452,7 @@
         <v>800</v>
       </c>
       <c r="S83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="T83" s="3">
         <v>900</v>
@@ -7265,7 +7464,7 @@
         <v>900</v>
       </c>
       <c r="W83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="X83" s="3">
         <v>1000</v>
@@ -7277,7 +7476,7 @@
         <v>1000</v>
       </c>
       <c r="AA83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="AB83" s="3">
         <v>1100</v>
@@ -7289,7 +7488,7 @@
         <v>1100</v>
       </c>
       <c r="AE83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AF83" s="3">
         <v>1200</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E89" s="3">
         <v>7900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8900</v>
-      </c>
-      <c r="N89" s="3">
-        <v>9200</v>
       </c>
       <c r="O89" s="3">
         <v>9200</v>
       </c>
       <c r="P89" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Q89" s="3">
         <v>8200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,67 +8144,68 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-200</v>
       </c>
       <c r="R91" s="3">
         <v>-200</v>
       </c>
       <c r="S91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
@@ -7993,37 +8214,40 @@
         <v>-100</v>
       </c>
       <c r="Y91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="Z91" s="3">
         <v>-300</v>
       </c>
       <c r="AA91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-77000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-105300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-45000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-37800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-38500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-130400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-159800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-121100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-196200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-18800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-23400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>11100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>16300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>32600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>3400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-24600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-29400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>2500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-21200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8376,22 +8610,22 @@
         <v>-1500</v>
       </c>
       <c r="J96" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="K96" s="3">
         <v>-1400</v>
       </c>
       <c r="L96" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="M96" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-1400</v>
       </c>
       <c r="N96" s="3">
         <v>-1400</v>
       </c>
       <c r="O96" s="3">
-        <v>-1200</v>
+        <v>-1400</v>
       </c>
       <c r="P96" s="3">
         <v>-1200</v>
@@ -8403,7 +8637,7 @@
         <v>-1200</v>
       </c>
       <c r="S96" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="T96" s="3">
         <v>-1300</v>
@@ -8424,7 +8658,7 @@
         <v>-1300</v>
       </c>
       <c r="Z96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="AA96" s="3">
         <v>-1200</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E100" s="3">
         <v>67900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>31100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>88100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>103200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-22300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>77500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>34200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-73600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>170700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>109700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>110200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>198900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>35100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>34200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-26600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>37000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-23700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>74400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-66200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E102" s="3">
         <v>58000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-38700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-35700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>38500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-34700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>48500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-41400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>10700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>22600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-24400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>29800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>16100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>79100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-25600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-61100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>51500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-61300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>28200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHMG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHMG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>CHMG</t>
   </si>
@@ -656,97 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E8" s="3">
         <v>27700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>25800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -777,40 +783,46 @@
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E10" s="3">
         <v>27700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>25300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>23700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +835,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,8 +868,11 @@
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +903,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -919,8 +938,11 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -937,10 +959,10 @@
         <v>500</v>
       </c>
       <c r="H15" s="3">
+        <v>500</v>
+      </c>
+      <c r="I15" s="3">
         <v>400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>500</v>
       </c>
       <c r="J15" s="3">
         <v>500</v>
@@ -951,8 +973,11 @@
       <c r="L15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +987,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17300</v>
+        <v>18100</v>
       </c>
       <c r="E17" s="3">
         <v>17300</v>
       </c>
       <c r="F17" s="3">
+        <v>17300</v>
+      </c>
+      <c r="G17" s="3">
         <v>16500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E18" s="3">
         <v>10400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,72 +1072,79 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>400</v>
       </c>
       <c r="F20" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G20" s="3">
         <v>500</v>
       </c>
       <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>500</v>
       </c>
       <c r="L20" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E21" s="3">
         <v>10500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1136,72 +1175,81 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E23" s="3">
         <v>10100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E24" s="3">
         <v>2300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1280,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E26" s="3">
         <v>7800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E27" s="3">
         <v>7700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6000</v>
       </c>
-      <c r="G27" s="3">
-        <v>5900</v>
-      </c>
       <c r="H27" s="3">
+        <v>6100</v>
+      </c>
+      <c r="I27" s="3">
         <v>5600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1385,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1420,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1455,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1490,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>-400</v>
       </c>
       <c r="F32" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="G32" s="3">
         <v>-500</v>
       </c>
       <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-500</v>
       </c>
       <c r="L32" s="3">
         <v>-500</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E33" s="3">
         <v>7800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1595,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E35" s="3">
         <v>7800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1687,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,72 +1702,79 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E41" s="3">
         <v>107600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>320100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>53400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>45400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>80400</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J41" s="3">
+        <v>70200</v>
+      </c>
+      <c r="K41" s="3">
         <v>94900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>75600</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E42" s="3">
         <v>18000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>20500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>23800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>19700</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>25400</v>
+      </c>
+      <c r="K42" s="3">
         <v>25800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>23900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1713,168 +1805,186 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E44" s="3">
         <v>200</v>
       </c>
       <c r="F44" s="3">
+        <v>200</v>
+      </c>
+      <c r="G44" s="3">
         <v>400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>600</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J44" s="3">
+        <v>700</v>
+      </c>
+      <c r="K44" s="3">
         <v>600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E45" s="3">
         <v>8600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7800</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K45" s="3">
         <v>8100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E46" s="3">
         <v>137500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>349300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>82500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>80000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>108500</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J46" s="3">
+        <v>104600</v>
+      </c>
+      <c r="K46" s="3">
         <v>129400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>69600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>291500</v>
+      </c>
+      <c r="E47" s="3">
         <v>287300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>296300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>538500</v>
       </c>
-      <c r="G47" s="3">
-        <v>542700</v>
-      </c>
       <c r="H47" s="3">
+        <v>544600</v>
+      </c>
+      <c r="I47" s="3">
         <v>560800</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J47" s="3">
+        <v>558300</v>
+      </c>
+      <c r="K47" s="3">
         <v>572100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>593300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>574900</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E48" s="3">
         <v>20300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20600</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J48" s="3">
-        <v>20200</v>
+        <v>20600</v>
       </c>
       <c r="K48" s="3">
         <v>20200</v>
       </c>
       <c r="L48" s="3">
+        <v>20200</v>
+      </c>
+      <c r="M48" s="3">
         <v>20900</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1894,7 +2004,7 @@
         <v>21800</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>21800</v>
       </c>
       <c r="J49" s="3">
         <v>21800</v>
@@ -1905,8 +2015,11 @@
       <c r="L49" s="3">
         <v>21800</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>21800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2050,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2085,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E52" s="3">
         <v>50900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>54700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>57200</v>
       </c>
-      <c r="G52" s="3">
-        <v>59800</v>
-      </c>
       <c r="H52" s="3">
+        <v>57900</v>
+      </c>
+      <c r="I52" s="3">
         <v>55000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J52" s="3">
+        <v>60100</v>
+      </c>
+      <c r="K52" s="3">
         <v>58200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>55400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>60700</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2155,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2710200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2696600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2852500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2796700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2776100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2774200</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J54" s="3">
+        <v>2755800</v>
+      </c>
+      <c r="K54" s="3">
         <v>2784900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2710500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2707800</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2207,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,72 +2222,79 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2270700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2358500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2469000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2433400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2396900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2451100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J57" s="3">
+        <v>2415900</v>
+      </c>
+      <c r="K57" s="3">
         <v>2480800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2429400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2473500</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E58" s="3">
         <v>62400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>118700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>106700</v>
       </c>
-      <c r="G58" s="3">
-        <v>134400</v>
-      </c>
       <c r="H58" s="3">
+        <v>133000</v>
+      </c>
+      <c r="I58" s="3">
         <v>20000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>106000</v>
+      </c>
+      <c r="K58" s="3">
         <v>26800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>55900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2189,77 +2325,86 @@
       <c r="L59" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2377100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2442500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2608800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2559800</v>
       </c>
-      <c r="G60" s="3">
-        <v>2531800</v>
-      </c>
       <c r="H60" s="3">
+        <v>2530300</v>
+      </c>
+      <c r="I60" s="3">
         <v>2493400</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J60" s="3">
+        <v>2544600</v>
+      </c>
+      <c r="K60" s="3">
         <v>2528900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2487500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2512300</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E61" s="3">
         <v>8300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8100</v>
       </c>
-      <c r="G61" s="3">
-        <v>8000</v>
-      </c>
       <c r="H61" s="3">
+        <v>9400</v>
+      </c>
+      <c r="I61" s="3">
         <v>59300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>9200</v>
+      </c>
+      <c r="K61" s="3">
         <v>58200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>500</v>
+        <v>27500</v>
       </c>
       <c r="E62" s="3">
         <v>500</v>
@@ -2268,25 +2413,28 @@
         <v>500</v>
       </c>
       <c r="G62" s="3">
+        <v>500</v>
+      </c>
+      <c r="H62" s="3">
         <v>21100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J62" s="3">
+        <v>800</v>
+      </c>
+      <c r="K62" s="3">
         <v>700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2465,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2500,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2535,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2455500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2451300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2617500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2568400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2560800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2553600</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J66" s="3">
+        <v>2554600</v>
+      </c>
+      <c r="K66" s="3">
         <v>2587800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2515300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2537800</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2587,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2620,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2655,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2690,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2725,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>256500</v>
+      </c>
+      <c r="E72" s="3">
         <v>250400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>244200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>252200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>247700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>243300</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J72" s="3">
+        <v>239000</v>
+      </c>
+      <c r="K72" s="3">
         <v>235500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>229900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>227600</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2795,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2830,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2865,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>254700</v>
+      </c>
+      <c r="E76" s="3">
         <v>245300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>235000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>228300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>215300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>220700</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J76" s="3">
+        <v>201200</v>
+      </c>
+      <c r="K76" s="3">
         <v>197100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>195200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>170100</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +2935,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E81" s="3">
         <v>7800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,22 +3027,23 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
-      </c>
-      <c r="E83" s="3">
-        <v>500</v>
       </c>
       <c r="F83" s="3">
         <v>500</v>
       </c>
       <c r="G83" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
@@ -2862,8 +3060,11 @@
       <c r="L83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3095,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3130,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3165,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3200,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3235,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E89" s="3">
         <v>12200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3287,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-400</v>
+        <v>-600</v>
       </c>
       <c r="E91" s="3">
         <v>-400</v>
       </c>
       <c r="F91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3355,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3390,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-71200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>208700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-42900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3442,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3219,7 +3452,7 @@
         <v>1600</v>
       </c>
       <c r="E96" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="F96" s="3">
         <v>1500</v>
@@ -3228,10 +3461,10 @@
         <v>1500</v>
       </c>
       <c r="H96" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I96" s="3">
         <v>2900</v>
-      </c>
-      <c r="I96" s="3">
-        <v>1500</v>
       </c>
       <c r="J96" s="3">
         <v>1500</v>
@@ -3242,8 +3475,11 @@
       <c r="L96" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3510,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3545,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3580,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-167100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>48200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-35400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>67900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3402,36 +3650,42 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-57500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-212400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>266600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-24600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>58000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>21400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHMG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHMG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>CHMG</t>
   </si>
@@ -656,103 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E8" s="3">
         <v>29400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>27700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -786,43 +793,49 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E10" s="3">
         <v>29400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>27700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +849,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,8 +885,11 @@
       <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +923,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,8 +961,11 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -962,10 +985,10 @@
         <v>500</v>
       </c>
       <c r="I15" s="3">
+        <v>500</v>
+      </c>
+      <c r="J15" s="3">
         <v>400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
@@ -976,8 +999,11 @@
       <c r="M15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,78 +1014,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E17" s="3">
         <v>18100</v>
-      </c>
-      <c r="E17" s="3">
-        <v>17300</v>
       </c>
       <c r="F17" s="3">
         <v>17300</v>
       </c>
       <c r="G17" s="3">
+        <v>17300</v>
+      </c>
+      <c r="H17" s="3">
         <v>16500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E18" s="3">
         <v>11300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,8 +1106,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1082,69 +1116,75 @@
         <v>300</v>
       </c>
       <c r="E20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
         <v>400</v>
       </c>
       <c r="G20" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H20" s="3">
         <v>500</v>
       </c>
       <c r="I20" s="3">
+        <v>500</v>
+      </c>
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>500</v>
       </c>
       <c r="M20" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E21" s="3">
         <v>11500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1178,78 +1218,87 @@
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E23" s="3">
         <v>11000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>3300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E26" s="3">
         <v>7700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E27" s="3">
         <v>7800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,8 +1560,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1502,69 +1572,75 @@
         <v>-300</v>
       </c>
       <c r="E32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
         <v>-400</v>
       </c>
       <c r="G32" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="H32" s="3">
         <v>-500</v>
       </c>
       <c r="I32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-500</v>
       </c>
       <c r="M32" s="3">
         <v>-500</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E33" s="3">
         <v>7700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E35" s="3">
         <v>7700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,78 +1789,85 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E41" s="3">
         <v>48500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>107600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>320100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>53400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>45400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>80400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>70200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>94900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>75600</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E42" s="3">
         <v>17300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>18700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>20500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>23800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>25400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>23900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1808,183 +1901,201 @@
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E44" s="3">
         <v>300</v>
-      </c>
-      <c r="E44" s="3">
-        <v>200</v>
       </c>
       <c r="F44" s="3">
         <v>200</v>
       </c>
       <c r="G44" s="3">
+        <v>200</v>
+      </c>
+      <c r="H44" s="3">
         <v>400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E45" s="3">
         <v>9300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E46" s="3">
         <v>79000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>137500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>349300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>82500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>80000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>108500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>104600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>129400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>69600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>285600</v>
+      </c>
+      <c r="E47" s="3">
         <v>291500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>287300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>296300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>538500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>544600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>560800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>558300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>572100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>593300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>574900</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E48" s="3">
         <v>20200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>20600</v>
       </c>
       <c r="J48" s="3">
         <v>20600</v>
       </c>
       <c r="K48" s="3">
-        <v>20200</v>
+        <v>20600</v>
       </c>
       <c r="L48" s="3">
         <v>20200</v>
       </c>
       <c r="M48" s="3">
+        <v>20200</v>
+      </c>
+      <c r="N48" s="3">
         <v>20900</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2018,8 +2129,11 @@
       <c r="M49" s="3">
         <v>21800</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>21800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,43 +2205,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E52" s="3">
         <v>52400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>50900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>54700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>57200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>57900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>55000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>60100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>58200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>55400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>60700</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2281,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2748700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2710200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2696600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2852500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2796700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2776100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2774200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2755800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2784900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2710500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2707800</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,78 +2353,85 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2313900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2270700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2358500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2469000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2433400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2396900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2451100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2415900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2480800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2429400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2473500</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>93800</v>
+      </c>
+      <c r="E58" s="3">
         <v>106000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>62400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>118700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>106700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>133000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>106000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>26800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>55900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2316,8 +2453,8 @@
       <c r="I59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J59" s="3">
-        <v>1500</v>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>1500</v>
@@ -2328,86 +2465,95 @@
       <c r="M59" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2433400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2377100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2442500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2608800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2559800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2530300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2493400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2544600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2528900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2487500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2512300</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E61" s="3">
         <v>50900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>59300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>58200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>27500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>500</v>
       </c>
       <c r="F62" s="3">
         <v>500</v>
@@ -2416,25 +2562,28 @@
         <v>500</v>
       </c>
       <c r="H62" s="3">
+        <v>500</v>
+      </c>
+      <c r="I62" s="3">
         <v>21100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>800</v>
       </c>
       <c r="J62" s="3">
         <v>800</v>
       </c>
       <c r="K62" s="3">
+        <v>800</v>
+      </c>
+      <c r="L62" s="3">
         <v>700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +2693,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2485800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2455500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2451300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2617500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2568400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2560800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2553600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2554600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2587800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2515300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2537800</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +2861,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +2899,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E72" s="3">
         <v>256500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>250400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>244200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>252200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>247700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>243300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>239000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>235500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>229900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>227600</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3051,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>262900</v>
+      </c>
+      <c r="E76" s="3">
         <v>254700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>245300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>235000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>228300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>215300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>220700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>201200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>197100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>195200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>170100</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E81" s="3">
         <v>7700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,25 +3226,26 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
         <v>600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>500</v>
       </c>
       <c r="G83" s="3">
         <v>500</v>
       </c>
       <c r="H83" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>700</v>
@@ -3063,8 +3262,11 @@
       <c r="M83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E89" s="3">
         <v>16300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,43 +3508,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-400</v>
       </c>
       <c r="F91" s="3">
         <v>-400</v>
       </c>
       <c r="G91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,43 +3620,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-71200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-57500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>208700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-42900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-28500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,8 +3676,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3455,7 +3689,7 @@
         <v>1600</v>
       </c>
       <c r="F96" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="G96" s="3">
         <v>1500</v>
@@ -3464,10 +3698,10 @@
         <v>1500</v>
       </c>
       <c r="I96" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J96" s="3">
         <v>2900</v>
-      </c>
-      <c r="J96" s="3">
-        <v>1500</v>
       </c>
       <c r="K96" s="3">
         <v>1500</v>
@@ -3478,8 +3712,11 @@
       <c r="M96" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,43 +3826,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-167100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>48200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-35400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>67900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3653,39 +3902,45 @@
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-57500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-212400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>266600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-24600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>58000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>21400</v>
       </c>
     </row>
